--- a/задание 1/задание 1.xlsx
+++ b/задание 1/задание 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zemlv\Desktop\sgm\Курсовая\задание 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CB39BC-2114-4937-9C71-5E0CAC36D8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAD81C6-D61D-4008-8A36-0C0CBA75A6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8AE0CAC0-9A32-4D52-8C57-38952320A0FB}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{8AE0CAC0-9A32-4D52-8C57-38952320A0FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
   <si>
     <t>x</t>
   </si>
@@ -340,7 +340,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -583,6 +583,19 @@
       </left>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -653,6 +666,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -677,38 +705,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1049,8 +1062,8 @@
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" customWidth="1"/>
-    <col min="16" max="18" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" customWidth="1"/>
+    <col min="15" max="18" width="9.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
@@ -1098,26 +1111,26 @@
         <v>26</v>
       </c>
       <c r="O4" s="1">
-        <v>1.2273000000000001</v>
-      </c>
-      <c r="P4" s="38" t="s">
+        <v>0.1827</v>
+      </c>
+      <c r="P4" s="17" t="s">
         <v>24</v>
       </c>
       <c r="Q4" s="18">
         <f>N9-N8</f>
-        <v>4.9999999999998934E-3</v>
+        <v>5.0000000000000044E-3</v>
       </c>
       <c r="S4" s="17" t="s">
         <v>34</v>
       </c>
       <c r="T4" s="18">
         <f>(O4-N10)/Q4</f>
-        <v>0.46000000000000357</v>
-      </c>
-      <c r="U4" s="46" t="s">
+        <v>-1.4599999999999989</v>
+      </c>
+      <c r="U4" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="V4" s="47"/>
+      <c r="V4" s="33"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
@@ -1131,17 +1144,17 @@
         <v>27</v>
       </c>
       <c r="O5" s="1">
-        <v>1.21</v>
+        <v>0.22420000000000001</v>
       </c>
       <c r="S5" s="17" t="s">
         <v>35</v>
       </c>
       <c r="T5" s="18">
         <f>(O5-N8)/Q4</f>
-        <v>-1.0000000000000444</v>
-      </c>
-      <c r="U5" s="46"/>
-      <c r="V5" s="47"/>
+        <v>8.8399999999999963</v>
+      </c>
+      <c r="U5" s="32"/>
+      <c r="V5" s="33"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
@@ -1151,10 +1164,10 @@
         <v>1.3011999999999999</v>
       </c>
       <c r="L6" s="8"/>
-      <c r="U6" s="45" t="s">
+      <c r="U6" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="V6" s="45"/>
+      <c r="V6" s="34"/>
     </row>
     <row r="7" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -1189,86 +1202,86 @@
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="L8" s="8"/>
       <c r="N8" s="26">
-        <v>1.2150000000000001</v>
-      </c>
-      <c r="O8" s="39">
-        <v>0.106044</v>
+        <v>0.18</v>
+      </c>
+      <c r="O8" s="30">
+        <v>5.6154299999999999</v>
       </c>
       <c r="P8" s="28">
         <f>O9-O8</f>
-        <v>7.2320000000000023E-3</v>
+        <v>-0.1485000000000003</v>
       </c>
       <c r="Q8" s="29">
         <f>P9-P8</f>
-        <v>-8.3700000000000441E-4</v>
+        <v>7.9100000000007498E-3</v>
       </c>
       <c r="R8" s="29">
         <f t="shared" ref="Q8:R15" si="0">Q9-Q8</f>
-        <v>9.4999999999997864E-5</v>
+        <v>-6.2000000000139721E-4</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L9" s="8"/>
       <c r="N9" s="26">
-        <v>1.22</v>
-      </c>
-      <c r="O9" s="39">
-        <v>0.113276</v>
+        <v>0.185</v>
+      </c>
+      <c r="O9" s="30">
+        <v>5.4669299999999996</v>
       </c>
       <c r="P9" s="28">
-        <f t="shared" ref="P8:P16" si="1">O10-O9</f>
-        <v>6.3949999999999979E-3</v>
+        <f t="shared" ref="P9:P17" si="1">O10-O9</f>
+        <v>-0.14058999999999955</v>
       </c>
       <c r="Q9" s="29">
         <f t="shared" si="0"/>
-        <v>-7.4200000000000654E-4</v>
+        <v>7.2899999999993526E-3</v>
       </c>
       <c r="R9" s="29">
         <f t="shared" si="0"/>
-        <v>9.3000000000023619E-5</v>
+        <v>-5.3999999999909676E-4</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="34" t="s">
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="36" t="s">
+      <c r="J10" s="41" t="s">
         <v>12</v>
       </c>
       <c r="L10" s="8"/>
       <c r="N10" s="26">
-        <v>1.2250000000000001</v>
-      </c>
-      <c r="O10" s="39">
-        <v>0.119671</v>
+        <v>0.19</v>
+      </c>
+      <c r="O10" s="30">
+        <v>5.3263400000000001</v>
       </c>
       <c r="P10" s="28">
         <f t="shared" si="1"/>
-        <v>5.6529999999999914E-3</v>
+        <v>-0.1333000000000002</v>
       </c>
       <c r="Q10" s="29">
         <f t="shared" si="0"/>
-        <v>-6.4899999999998292E-4</v>
+        <v>6.7500000000002558E-3</v>
       </c>
       <c r="R10" s="29">
         <f t="shared" si="0"/>
-        <v>9.2999999999981986E-5</v>
+        <v>-5.0000000000061107E-4</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="32"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="22" t="s">
         <v>4</v>
       </c>
@@ -1290,26 +1303,26 @@
       <c r="H11" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="I11" s="35"/>
-      <c r="J11" s="37"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="42"/>
       <c r="L11" s="8"/>
       <c r="N11" s="26">
-        <v>1.23</v>
-      </c>
-      <c r="O11" s="39">
-        <v>0.12532399999999999</v>
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="O11" s="30">
+        <v>5.1930399999999999</v>
       </c>
       <c r="P11" s="28">
         <f t="shared" si="1"/>
-        <v>5.0040000000000084E-3</v>
+        <v>-0.12654999999999994</v>
       </c>
       <c r="Q11" s="29">
         <f t="shared" si="0"/>
-        <v>-5.5600000000000094E-4</v>
+        <v>6.2499999999996447E-3</v>
       </c>
       <c r="R11" s="29">
         <f t="shared" si="0"/>
-        <v>9.0999999999979986E-5</v>
+        <v>-4.3999999999932982E-4</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -1353,22 +1366,22 @@
       </c>
       <c r="L12" s="8"/>
       <c r="N12" s="26">
-        <v>1.2350000000000001</v>
-      </c>
-      <c r="O12" s="39">
-        <v>0.130328</v>
+        <v>0.2</v>
+      </c>
+      <c r="O12" s="30">
+        <v>5.0664899999999999</v>
       </c>
       <c r="P12" s="28">
         <f t="shared" si="1"/>
-        <v>4.4480000000000075E-3</v>
+        <v>-0.1203000000000003</v>
       </c>
       <c r="Q12" s="29">
         <f t="shared" si="0"/>
-        <v>-4.6500000000002095E-4</v>
+        <v>5.8100000000003149E-3</v>
       </c>
       <c r="R12" s="29">
         <f t="shared" si="0"/>
-        <v>9.0000000000034497E-5</v>
+        <v>-4.0999999999957737E-4</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
@@ -1412,22 +1425,22 @@
       </c>
       <c r="L13" s="8"/>
       <c r="N13" s="26">
-        <v>1.24</v>
-      </c>
-      <c r="O13" s="39">
-        <v>0.13477600000000001</v>
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="O13" s="30">
+        <v>4.9461899999999996</v>
       </c>
       <c r="P13" s="28">
         <f t="shared" si="1"/>
-        <v>3.9829999999999866E-3</v>
+        <v>-0.11448999999999998</v>
       </c>
       <c r="Q13" s="29">
         <f t="shared" si="0"/>
-        <v>-3.7499999999998646E-4</v>
+        <v>5.4000000000007375E-3</v>
       </c>
       <c r="R13" s="29">
         <f t="shared" si="0"/>
-        <v>8.8000000000004741E-5</v>
+        <v>-3.7000000000197986E-4</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1471,22 +1484,22 @@
       </c>
       <c r="L14" s="8"/>
       <c r="N14" s="26">
-        <v>1.2450000000000001</v>
-      </c>
-      <c r="O14" s="39">
-        <v>0.13875899999999999</v>
+        <v>0.21</v>
+      </c>
+      <c r="O14" s="30">
+        <v>4.8316999999999997</v>
       </c>
       <c r="P14" s="28">
         <f t="shared" si="1"/>
-        <v>3.6080000000000001E-3</v>
+        <v>-0.10908999999999924</v>
       </c>
       <c r="Q14" s="29">
         <f t="shared" si="0"/>
-        <v>-2.8699999999998171E-4</v>
+        <v>5.0299999999987577E-3</v>
       </c>
       <c r="R14" s="29">
         <f t="shared" si="0"/>
-        <v>8.699999999994823E-5</v>
+        <v>-3.2999999999816509E-4</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
@@ -1530,21 +1543,22 @@
       </c>
       <c r="L15" s="8"/>
       <c r="N15" s="26">
-        <v>1.25</v>
-      </c>
-      <c r="O15" s="39">
-        <v>0.14236699999999999</v>
+        <v>0.215</v>
+      </c>
+      <c r="O15" s="30">
+        <v>4.7226100000000004</v>
       </c>
       <c r="P15" s="28">
         <f t="shared" si="1"/>
-        <v>3.3210000000000184E-3</v>
+        <v>-0.10406000000000049</v>
       </c>
       <c r="Q15" s="29">
         <f>P16-P15</f>
-        <v>-2.0000000000003348E-4</v>
-      </c>
-      <c r="R15" s="28" t="s">
-        <v>33</v>
+        <v>4.7000000000005926E-3</v>
+      </c>
+      <c r="R15" s="29">
+        <f t="shared" si="0"/>
+        <v>-3.1000000000069861E-4</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
@@ -1588,23 +1602,22 @@
       </c>
       <c r="L16" s="8"/>
       <c r="N16" s="26">
-        <v>1.2549999999999999</v>
-      </c>
-      <c r="O16" s="39">
-        <v>0.14568800000000001</v>
+        <v>0.22</v>
+      </c>
+      <c r="O16" s="30">
+        <v>4.6185499999999999</v>
       </c>
       <c r="P16" s="28">
         <f t="shared" si="1"/>
-        <v>3.1209999999999849E-3</v>
-      </c>
-      <c r="Q16" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" s="28" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>-9.9359999999999893E-2</v>
+      </c>
+      <c r="Q16" s="29">
+        <f>P17-P16</f>
+        <v>4.389999999999894E-3</v>
+      </c>
+      <c r="R16" s="28"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>5</v>
       </c>
@@ -1644,42 +1657,30 @@
         <v>13971.742543171125</v>
       </c>
       <c r="L17" s="8"/>
-      <c r="N17" s="42">
-        <v>1.26</v>
-      </c>
-      <c r="O17" s="43">
-        <v>0.148809</v>
-      </c>
-      <c r="P17" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q17" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="R17" s="44" t="s">
-        <v>33</v>
-      </c>
+      <c r="N17" s="43">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="O17" s="44">
+        <v>4.51919</v>
+      </c>
+      <c r="P17" s="28">
+        <f>O18-O17</f>
+        <v>-9.4969999999999999E-2</v>
+      </c>
+      <c r="Q17" s="45"/>
+      <c r="R17" s="45"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L18" s="8"/>
-      <c r="N18" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="O18" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="P18" s="41">
-        <f>SUM(P8:P16)</f>
-        <v>4.2764999999999997E-2</v>
-      </c>
-      <c r="Q18" s="41">
-        <f t="shared" ref="Q18:R18" si="11">SUM(Q8:Q16)</f>
-        <v>-4.1110000000000174E-3</v>
-      </c>
-      <c r="R18" s="41">
-        <f t="shared" si="11"/>
-        <v>6.3699999999997092E-4</v>
-      </c>
+      <c r="N18" s="46">
+        <v>0.23</v>
+      </c>
+      <c r="O18" s="47">
+        <v>4.42422</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
@@ -1697,27 +1698,45 @@
         <v>-0.32727413681823236</v>
       </c>
       <c r="L19" s="8"/>
-      <c r="N19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O19" s="29">
-        <f>O17-O8</f>
-        <v>4.2764999999999997E-2</v>
-      </c>
-      <c r="P19" s="29">
-        <f>P16-P8</f>
-        <v>-4.1110000000000174E-3</v>
-      </c>
-      <c r="Q19" s="29">
-        <f>Q15-Q8</f>
-        <v>6.3699999999997092E-4</v>
-      </c>
-      <c r="R19" s="28" t="s">
+      <c r="N19" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" s="28" t="s">
         <v>33</v>
+      </c>
+      <c r="P19" s="28">
+        <f>SUM(P8:P17)</f>
+        <v>-1.1912099999999999</v>
+      </c>
+      <c r="Q19" s="28">
+        <f>SUM(Q8:Q16)</f>
+        <v>5.35300000000003E-2</v>
+      </c>
+      <c r="R19" s="28">
+        <f>SUM(R8:R16)</f>
+        <v>-3.5200000000008558E-3</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L20" s="8"/>
+      <c r="N20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O20" s="29">
+        <f>O18-O8</f>
+        <v>-1.1912099999999999</v>
+      </c>
+      <c r="P20" s="29">
+        <f>P17-P8</f>
+        <v>5.35300000000003E-2</v>
+      </c>
+      <c r="Q20" s="29">
+        <f>Q16-Q8</f>
+        <v>-3.5200000000008558E-3</v>
+      </c>
+      <c r="R20" s="28" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
@@ -1728,20 +1747,6 @@
         <v>6.3932746944522382E-9</v>
       </c>
       <c r="L21" s="8"/>
-      <c r="N21" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O21" s="5">
-        <f>O8+T5*P8+(O8*(T5-1)/2)*Q8+(T5*(T5-1)*(T5-2)/6)*R8</f>
-        <v>9.8805758827999662E-2</v>
-      </c>
-      <c r="P21" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q21" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="R21" s="48"/>
     </row>
     <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6"/>
@@ -1756,24 +1761,38 @@
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="7"/>
-      <c r="Q22" s="48"/>
-      <c r="R22" s="48"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L23" s="8"/>
-      <c r="Q23" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="R23" s="45"/>
+      <c r="N23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O23" s="5">
+        <f>O8+T5*P8+(O8*(T5-1)/2)*Q8+(T5*(T5-1)*(T5-2)/6)*R8</f>
+        <v>4.4278235630159042</v>
+      </c>
+      <c r="P23" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q23" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="R23" s="33"/>
     </row>
     <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D24" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L24" s="8"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="33"/>
     </row>
     <row r="25" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="L25" s="8"/>
+      <c r="Q25" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="R25" s="31"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L26" s="8"/>
@@ -1810,25 +1829,25 @@
         <v>0</v>
       </c>
       <c r="B29" s="12">
-        <v>0.02</v>
+        <v>0.115</v>
       </c>
       <c r="C29" s="12">
-        <v>1.0231600000000001</v>
+        <v>8.6572899999999997</v>
       </c>
       <c r="D29" s="12">
-        <f t="shared" ref="D29:D34" si="12">$E$37-A29</f>
-        <v>1.75</v>
+        <f t="shared" ref="D29:D34" si="11">$E$37-A29</f>
+        <v>1.6400000000000028</v>
       </c>
       <c r="E29" s="12">
         <v>-120</v>
       </c>
       <c r="F29" s="12">
         <f>D29*E29</f>
-        <v>-210</v>
+        <v>-196.80000000000032</v>
       </c>
       <c r="G29" s="12">
         <f>C29/F29</f>
-        <v>-4.8721904761904761E-3</v>
+        <v>-4.3990294715447083E-2</v>
       </c>
       <c r="L29" s="8"/>
     </row>
@@ -1837,25 +1856,25 @@
         <v>1</v>
       </c>
       <c r="B30" s="1">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="C30" s="1">
-        <v>1.0959000000000001</v>
+        <v>8.2932900000000007</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" si="12"/>
-        <v>0.75</v>
+        <f t="shared" si="11"/>
+        <v>0.64000000000000279</v>
       </c>
       <c r="E30" s="1">
         <v>24</v>
       </c>
       <c r="F30" s="1">
-        <f t="shared" ref="F30:F34" si="13">D30*E30</f>
-        <v>18</v>
+        <f t="shared" ref="F30:F34" si="12">D30*E30</f>
+        <v>15.360000000000067</v>
       </c>
       <c r="G30" s="1">
-        <f t="shared" ref="G30:G33" si="14">C30/F30</f>
-        <v>6.0883333333333338E-2</v>
+        <f t="shared" ref="G30:G33" si="13">C30/F30</f>
+        <v>0.53992773437499775</v>
       </c>
       <c r="L30" s="8"/>
     </row>
@@ -1864,25 +1883,25 @@
         <v>2</v>
       </c>
       <c r="B31" s="1">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="C31" s="1">
-        <v>1.1472500000000001</v>
+        <v>7.9582899999999999</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="12"/>
-        <v>-0.25</v>
+        <f t="shared" si="11"/>
+        <v>-0.35999999999999721</v>
       </c>
       <c r="E31" s="1">
         <v>-12</v>
       </c>
       <c r="F31" s="1">
+        <f t="shared" si="12"/>
+        <v>4.3199999999999665</v>
+      </c>
+      <c r="G31" s="1">
         <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
-      <c r="G31" s="1">
-        <f t="shared" si="14"/>
-        <v>0.38241666666666668</v>
+        <v>1.8421967592592734</v>
       </c>
       <c r="L31" s="8"/>
     </row>
@@ -1891,25 +1910,25 @@
         <v>3</v>
       </c>
       <c r="B32" s="1">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="C32" s="1">
-        <v>1.2148300000000001</v>
+        <v>7.64893</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="12"/>
-        <v>-1.25</v>
+        <f t="shared" si="11"/>
+        <v>-1.3599999999999972</v>
       </c>
       <c r="E32" s="1">
         <v>12</v>
       </c>
       <c r="F32" s="1">
+        <f t="shared" si="12"/>
+        <v>-16.319999999999965</v>
+      </c>
+      <c r="G32" s="1">
         <f t="shared" si="13"/>
-        <v>-15</v>
-      </c>
-      <c r="G32" s="1">
-        <f t="shared" si="14"/>
-        <v>-8.0988666666666667E-2</v>
+        <v>-0.46868443627451084</v>
       </c>
       <c r="L32" s="8"/>
     </row>
@@ -1918,25 +1937,25 @@
         <v>4</v>
       </c>
       <c r="B33" s="1">
-        <v>0.23</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="C33" s="1">
-        <v>1.3011999999999999</v>
+        <v>7.3623500000000002</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="12"/>
-        <v>-2.25</v>
+        <f t="shared" si="11"/>
+        <v>-2.3599999999999972</v>
       </c>
       <c r="E33" s="1">
         <v>-24</v>
       </c>
       <c r="F33" s="1">
+        <f t="shared" si="12"/>
+        <v>56.63999999999993</v>
+      </c>
+      <c r="G33" s="1">
         <f t="shared" si="13"/>
-        <v>54</v>
-      </c>
-      <c r="G33" s="1">
-        <f t="shared" si="14"/>
-        <v>2.4096296296296296E-2</v>
+        <v>0.12998499293785326</v>
       </c>
       <c r="L33" s="8"/>
     </row>
@@ -1945,25 +1964,25 @@
         <v>5</v>
       </c>
       <c r="B34" s="1">
-        <v>0.3</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C34" s="1">
-        <v>1.4097599999999999</v>
+        <v>7.0961299999999996</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" si="12"/>
-        <v>-3.25</v>
+        <f t="shared" si="11"/>
+        <v>-3.3599999999999972</v>
       </c>
       <c r="E34" s="1">
         <v>120</v>
       </c>
       <c r="F34" s="1">
-        <f t="shared" si="13"/>
-        <v>-390</v>
+        <f t="shared" si="12"/>
+        <v>-403.19999999999965</v>
       </c>
       <c r="G34" s="1">
         <f>C34/F34</f>
-        <v>-3.6147692307692304E-3</v>
+        <v>-1.7599528769841284E-2</v>
       </c>
       <c r="L34" s="8"/>
     </row>
@@ -1975,14 +1994,14 @@
         <v>2</v>
       </c>
       <c r="B36" s="20">
-        <v>0.125</v>
+        <v>0.1232</v>
       </c>
       <c r="D36" s="17" t="s">
         <v>24</v>
       </c>
       <c r="E36" s="18">
         <f>B30-B29</f>
-        <v>0.06</v>
+        <v>4.9999999999999906E-3</v>
       </c>
       <c r="L36" s="8"/>
     </row>
@@ -1992,7 +2011,7 @@
       </c>
       <c r="E37" s="18">
         <f>(B36-B29)/E36</f>
-        <v>1.75</v>
+        <v>1.6400000000000028</v>
       </c>
       <c r="L37" s="8"/>
     </row>
@@ -2005,19 +2024,19 @@
       </c>
       <c r="B39" s="1">
         <f>PRODUCT(D29:D34)</f>
-        <v>2.999267578125</v>
-      </c>
-      <c r="D39" s="30" t="s">
+        <v>4.0748958351359761</v>
+      </c>
+      <c r="D39" s="35" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="1">
         <f>SUM(G29:G34)</f>
-        <v>0.37792066992266993</v>
+        <v>1.9818352268123252</v>
       </c>
       <c r="L39" s="8"/>
     </row>
     <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D40" s="30"/>
+      <c r="D40" s="35"/>
       <c r="L40" s="8"/>
     </row>
     <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2026,7 +2045,7 @@
       </c>
       <c r="B41" s="5">
         <f>B39*E39</f>
-        <v>1.1334852124023438</v>
+        <v>8.0757721116633068</v>
       </c>
       <c r="L41" s="8"/>
     </row>
@@ -2043,16 +2062,15 @@
       <c r="L45" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="U4:V5"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="Q21:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="D39:D40"/>
+  <mergeCells count="8">
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="J10:J11"/>
+    <mergeCell ref="U4:V5"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="Q23:R24"/>
+    <mergeCell ref="D39:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
